--- a/demandas.xlsx
+++ b/demandas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30327"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://trten-my.sharepoint.com/personal/lucas_machado_thomsonreuters_com/Documents/Desktop/Ven/tr-intelligence/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://trten-my.sharepoint.com/personal/larissa_rosso_thomsonreuters_com/Documents/Larissa - Campinas/BI - Regional Camp/gerência/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{146EC067-3D73-4BA5-96E3-DEC34EB2C8E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4F018D40-D7D9-4A50-BE34-EC90B5486953}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EAC1ED43-0C1F-4B8F-A60B-D2518409BADF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="795" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -183,6 +183,12 @@
     <t>Rodrigo Soares (RIO), Giacomo Urbini (SP Interior), Gabriel Monteiro (SP Interior)</t>
   </si>
   <si>
+    <t>Felipe Leite Dalpino von Scheibler</t>
+  </si>
+  <si>
+    <t>Pedro Souza</t>
+  </si>
+  <si>
     <t>Disponibilidade</t>
   </si>
   <si>
@@ -190,19 +196,13 @@
   </si>
   <si>
     <t>Sim</t>
-  </si>
-  <si>
-    <t>Time Bárbara Arabe - avaliar e lançar posteriormente o nome</t>
-  </si>
-  <si>
-    <t/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -217,6 +217,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -239,7 +245,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -247,12 +253,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -280,79 +301,77 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="20">
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+  <dxfs count="19">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ hh:mm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ hh:mm"/>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="27" formatCode="m/d/yyyy\ h:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="27" formatCode="m/d/yyyy\ h:mm"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -383,124 +402,126 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9EE55BBE-7633-4BB8-A8C3-8CBFD10515C0}" name="Tabela1" displayName="Tabela1" ref="A1:T6" totalsRowShown="0">
-  <autoFilter ref="A1:T6" xr:uid="{9EE55BBE-7633-4BB8-A8C3-8CBFD10515C0}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9EE55BBE-7633-4BB8-A8C3-8CBFD10515C0}" name="Tabela1" displayName="Tabela1" ref="A1:T7" totalsRowShown="0">
+  <autoFilter ref="A1:T7" xr:uid="{9EE55BBE-7633-4BB8-A8C3-8CBFD10515C0}"/>
   <tableColumns count="20">
-    <tableColumn id="1" xr3:uid="{CB769E80-F56D-44A4-BD76-9ECBF144B0BE}" name="ID" dataDxfId="19">
+    <tableColumn id="1" xr3:uid="{CB769E80-F56D-44A4-BD76-9ECBF144B0BE}" name="ID" dataDxfId="18">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="id"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{4D8B106F-95AD-4D8E-AAB6-36E9F23386C5}" name="Hora de início" dataDxfId="18">
+    <tableColumn id="2" xr3:uid="{4D8B106F-95AD-4D8E-AAB6-36E9F23386C5}" name="Hora de início" dataDxfId="17">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="startDate"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{75FE9123-26DF-4B74-B2D9-6CC5981F646A}" name="Hora da conclusão" dataDxfId="17">
+    <tableColumn id="3" xr3:uid="{75FE9123-26DF-4B74-B2D9-6CC5981F646A}" name="Hora da conclusão" dataDxfId="16">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="submitDate"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{A577DE9E-FDD9-4669-B367-3CB72F6E44EE}" name="Email" dataDxfId="16">
+    <tableColumn id="4" xr3:uid="{A577DE9E-FDD9-4669-B367-3CB72F6E44EE}" name="Email" dataDxfId="15">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="responder"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{0C6E2F69-3C5E-4723-8874-35E442A3B566}" name="Nome" dataDxfId="15">
+    <tableColumn id="5" xr3:uid="{0C6E2F69-3C5E-4723-8874-35E442A3B566}" name="Nome" dataDxfId="14">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="responderName"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{03474AC7-417E-4FC4-9AC8-CC956DDE6CD4}" name="Qual sua necessidade?" dataDxfId="14">
+    <tableColumn id="6" xr3:uid="{03474AC7-417E-4FC4-9AC8-CC956DDE6CD4}" name="Qual sua necessidade?" dataDxfId="13">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r6546689247a6419080a77d70a9210618"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{AECB7460-EA6F-45FE-9518-ECA5AC28CCB5}" name="Qual a data de entrada?" dataDxfId="13">
+    <tableColumn id="8" xr3:uid="{AECB7460-EA6F-45FE-9518-ECA5AC28CCB5}" name="Qual a data de entrada?" dataDxfId="12">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r6f2f890f3cde41078cfc13e1b0da6bca"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{4847C9F7-1C84-42BF-B899-0C00F71CEF46}" name="Qual o níveis" dataDxfId="12">
+    <tableColumn id="9" xr3:uid="{4847C9F7-1C84-42BF-B899-0C00F71CEF46}" name="Qual o níveis" dataDxfId="11">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r9a4981c0cd334f0aa8105a50db1a3368"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{75482E00-2946-414C-B612-52C3F315CBBF}" name="Quais são os nomes:" dataDxfId="11">
+    <tableColumn id="7" xr3:uid="{75482E00-2946-414C-B612-52C3F315CBBF}" name="Quais são os nomes:" dataDxfId="10">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r664896e9ec9b4777b0eb7cdf0093bc3e"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{FF519106-1E29-42CE-8810-7526479DCB21}" name="Quantas pessoas:" dataDxfId="10">
+    <tableColumn id="14" xr3:uid="{FF519106-1E29-42CE-8810-7526479DCB21}" name="Quantas pessoas:" dataDxfId="9">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rd3e80f5eaa114b97b6807b1250086785"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{599F8A8E-A9C4-4D43-A04C-7C99D70659EE}" name="Quais os nomes" dataDxfId="9">
+    <tableColumn id="15" xr3:uid="{599F8A8E-A9C4-4D43-A04C-7C99D70659EE}" name="Quais os nomes" dataDxfId="8">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rcaab62f2261d42ac994dc8ebaf9d29a3"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{BEEC76D8-E404-4659-B947-67B0BA4387AF}" name="Quantas pessoas são?" dataDxfId="8">
+    <tableColumn id="10" xr3:uid="{BEEC76D8-E404-4659-B947-67B0BA4387AF}" name="Quantas pessoas são?" dataDxfId="7">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="re4c778be6490461283996a62d008c59c"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{BB54D31C-8725-4B7D-8D02-5B9CA56BC54C}" name="Qual produto referente ao treinamento?" dataDxfId="7">
+    <tableColumn id="11" xr3:uid="{BB54D31C-8725-4B7D-8D02-5B9CA56BC54C}" name="Qual produto referente ao treinamento?" dataDxfId="6">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="ra18e674be005484b8ec2ed6cf8b9838b"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{3505AB15-9417-4566-8FCF-5D7BB16E03F2}" name="Qual assunto do treinamento?" dataDxfId="6">
+    <tableColumn id="12" xr3:uid="{3505AB15-9417-4566-8FCF-5D7BB16E03F2}" name="Qual assunto do treinamento?" dataDxfId="5">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rc7895b2189cf44d793c7c4ed234acc1b"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{2FA870AD-B892-47CE-8988-2555008350D6}" name="Detalhe sua necessidade:" dataDxfId="5">
+    <tableColumn id="13" xr3:uid="{2FA870AD-B892-47CE-8988-2555008350D6}" name="Detalhe sua necessidade:" dataDxfId="4">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r19325c28b61d4ce586d44443465f3cd6"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="24" xr3:uid="{673BE25E-4985-4AD8-A523-0DFDCD2FBB14}" name="Data início" dataDxfId="4"/>
-    <tableColumn id="18" xr3:uid="{DABE99D8-C191-4D49-87D1-13330FF0CEC4}" name="Data finalizado" dataDxfId="3"/>
-    <tableColumn id="21" xr3:uid="{DF20E221-F993-454B-A831-8AF7A1FCD4B3}" name="Assunto" dataDxfId="2"/>
+    <tableColumn id="24" xr3:uid="{673BE25E-4985-4AD8-A523-0DFDCD2FBB14}" name="Data início" dataDxfId="3"/>
+    <tableColumn id="18" xr3:uid="{DABE99D8-C191-4D49-87D1-13330FF0CEC4}" name="Data finalizado" dataDxfId="2"/>
+    <tableColumn id="21" xr3:uid="{DF20E221-F993-454B-A831-8AF7A1FCD4B3}" name="Assunto"/>
     <tableColumn id="16" xr3:uid="{E16FB392-D3E3-478E-BCB1-2F678FF016C9}" name="Detalhe assunto" dataDxfId="1"/>
-    <tableColumn id="17" xr3:uid="{92C94EC1-8D6D-4447-812D-2309B2DB014C}" name="Região" dataDxfId="0"/>
+    <tableColumn id="17" xr3:uid="{92C94EC1-8D6D-4447-812D-2309B2DB014C}" name="Região" dataDxfId="0">
+      <calculatedColumnFormula>IF(_xlfn.XLOOKUP(Tabela1[[#This Row],[Nome]],Base!B:B,Base!C:C,0)=0,"",_xlfn.XLOOKUP(Tabela1[[#This Row],[Nome]],Base!B:B,Base!C:C,0))</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="ZLjMYhpqXUuOHDl97BqCWCUrcjkuX0VJr631t9XjA3pUOExPWkxCNzBQQ1VINEg2RU9POThONkRYVC4u" isFormConnected="1" maxResponseId="7" latestEventMarker="45">
+      <xlmsforms:msForm id="ZLjMYhpqXUuOHDl97BqCWCUrcjkuX0VJr631t9XjA3pUOExPWkxCNzBQQ1VINEg2RU9POThONkRYVC4u" isFormConnected="1" maxResponseId="10" latestEventMarker="48">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -799,7 +820,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -808,9 +829,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BBC0694-BED0-424C-986E-E37AEEF52857}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -818,7 +839,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -826,7 +847,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -834,7 +855,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="B4" s="8"/>
     </row>
   </sheetData>
@@ -850,13 +871,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5894F219-A53F-46E8-ACD7-65F9A9065197}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="14.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -867,7 +888,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="B2" t="s">
         <v>9</v>
       </c>
@@ -875,7 +896,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="B3" t="s">
         <v>11</v>
       </c>
@@ -883,7 +904,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="B4" t="s">
         <v>13</v>
       </c>
@@ -891,7 +912,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="B5" t="s">
         <v>15</v>
       </c>
@@ -909,18 +930,18 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB99AD98-1882-4D74-8F3F-3E7C72A578B2}">
-  <dimension ref="A1:T6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:T7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="33.7109375" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="26.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.140625" style="3" customWidth="1"/>
     <col min="8" max="8" width="14.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="39" style="3" customWidth="1"/>
     <col min="10" max="10" width="10.5703125" style="3" customWidth="1"/>
     <col min="11" max="11" width="27.5703125" style="3" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.85546875" style="3" customWidth="1"/>
@@ -933,7 +954,7 @@
     <col min="19" max="19" width="33.28515625" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" ht="42.75" customHeight="1">
       <c r="A1" t="s">
         <v>17</v>
       </c>
@@ -995,7 +1016,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20">
       <c r="A2">
         <v>5</v>
       </c>
@@ -1029,11 +1050,12 @@
       <c r="Q2" s="2">
         <v>46199</v>
       </c>
-      <c r="T2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T2" t="str">
+        <f>IF(_xlfn.XLOOKUP(Tabela1[[#This Row],[Nome]],Base!B:B,Base!C:C,0)=0,"",_xlfn.XLOOKUP(Tabela1[[#This Row],[Nome]],Base!B:B,Base!C:C,0))</f>
+        <v>Larissa</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20">
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="G3" s="2"/>
@@ -1043,11 +1065,12 @@
       <c r="Q3" s="2">
         <v>46196</v>
       </c>
-      <c r="T3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T3" t="str">
+        <f>IF(_xlfn.XLOOKUP(Tabela1[[#This Row],[Nome]],Base!B:B,Base!C:C,0)=0,"",_xlfn.XLOOKUP(Tabela1[[#This Row],[Nome]],Base!B:B,Base!C:C,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:20">
       <c r="A4">
         <v>6</v>
       </c>
@@ -1085,17 +1108,14 @@
       <c r="O4" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="P4" s="2">
-        <v>46209</v>
-      </c>
-      <c r="Q4" s="2">
-        <v>46227</v>
-      </c>
-      <c r="T4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="T4" t="str">
+        <f>IF(_xlfn.XLOOKUP(Tabela1[[#This Row],[Nome]],Base!B:B,Base!C:C,0)=0,"",_xlfn.XLOOKUP(Tabela1[[#This Row],[Nome]],Base!B:B,Base!C:C,0))</f>
+        <v>SP</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20">
       <c r="A5">
         <v>7</v>
       </c>
@@ -1124,12 +1144,18 @@
       <c r="L5" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="P5" s="2"/>
-      <c r="T5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="P5" s="2">
+        <v>46209</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>46220</v>
+      </c>
+      <c r="T5" t="str">
+        <f>IF(_xlfn.XLOOKUP(Tabela1[[#This Row],[Nome]],Base!B:B,Base!C:C,0)=0,"",_xlfn.XLOOKUP(Tabela1[[#This Row],[Nome]],Base!B:B,Base!C:C,0))</f>
+        <v>Larissa</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20">
       <c r="A6">
         <v>8</v>
       </c>
@@ -1151,16 +1177,57 @@
       <c r="G6" s="2">
         <v>46237</v>
       </c>
-      <c r="I6" s="3" t="s">
-        <v>50</v>
+      <c r="I6" s="11" t="s">
+        <v>47</v>
       </c>
       <c r="J6" s="9"/>
       <c r="L6" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="P6" s="2"/>
-      <c r="T6" t="s">
-        <v>14</v>
+      <c r="P6" s="2">
+        <v>46237</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>46248</v>
+      </c>
+      <c r="T6" t="str">
+        <f>IF(_xlfn.XLOOKUP(Tabela1[[#This Row],[Nome]],Base!B:B,Base!C:C,0)=0,"",_xlfn.XLOOKUP(Tabela1[[#This Row],[Nome]],Base!B:B,Base!C:C,0))</f>
+        <v>Larissa</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20">
+      <c r="A7">
+        <v>10</v>
+      </c>
+      <c r="B7" s="1">
+        <v>46220.717777777798</v>
+      </c>
+      <c r="C7" s="1">
+        <v>46220.718020833301</v>
+      </c>
+      <c r="D7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" s="2">
+        <v>46237</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="J7" s="9"/>
+      <c r="L7" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="P7" s="2"/>
+      <c r="T7" t="str">
+        <f>IF(_xlfn.XLOOKUP(Tabela1[[#This Row],[Nome]],Base!B:B,Base!C:C,0)=0,"",_xlfn.XLOOKUP(Tabela1[[#This Row],[Nome]],Base!B:B,Base!C:C,0))</f>
+        <v>Larissa</v>
       </c>
     </row>
   </sheetData>
@@ -1174,27 +1241,27 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6061613-27EE-484F-B660-18905F0B4D02}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.140625" customWidth="1"/>
     <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B1" t="s">
         <v>30</v>
       </c>
       <c r="C1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
